--- a/public/exports/31210917.xlsx
+++ b/public/exports/31210917.xlsx
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">5128072</t>
+          <t xml:space="preserve">736938, 5125209</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>548</v>
+        <v>1444</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5131186</t>
+          <t xml:space="preserve">7553965</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -290,7 +290,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">736938, 5125209</t>
+          <t xml:space="preserve">7553965</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F7">
-        <v>1444</v>
+        <v>830</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,16 +381,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7553965</t>
+          <t xml:space="preserve">7838419</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F8">
-        <v>254</v>
+        <v>7336</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7553965</t>
+          <t xml:space="preserve">7838419</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F9">
-        <v>830</v>
+        <v>462</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7838419</t>
+          <t xml:space="preserve">9986379</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F10">
-        <v>7336</v>
+        <v>2031</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,30 +531,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7838419</t>
+          <t xml:space="preserve">7553965</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F11">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310040038</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-05-15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">9986379</t>
+          <t xml:space="preserve">5128072</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -590,21 +590,21 @@
         </is>
       </c>
       <c r="F12">
-        <v>2031</v>
+        <v>548</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310040572</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2023-05-20</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7553965</t>
+          <t xml:space="preserve">5131186</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F13">
-        <v>455</v>
+        <v>262</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">310040038</t>
+          <t xml:space="preserve">310040585</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-15</t>
+          <t xml:space="preserve">2023-05-20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">310040579</t>
+          <t xml:space="preserve">311001996</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-05-20</t>
+          <t xml:space="preserve">2023-06-05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">

--- a/public/exports/31210917.xlsx
+++ b/public/exports/31210917.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -29,35 +29,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Adresse</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postnr.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -81,33 +91,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Landevejen 41</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">100061714</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>429</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -131,33 +151,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Lodsvej 22A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">5124834</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>1099</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -181,33 +211,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Midtbjergevej 3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">5125209</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>1416</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -231,33 +271,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">736938, 5125209</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>1444</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -281,33 +331,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">7553965</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>254</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -331,33 +391,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">7553965</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="H7">
         <v>830</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -381,33 +451,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">7838419</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F8">
+      <c r="H8">
         <v>7336</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -431,33 +511,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 19</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t xml:space="preserve">7838419</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="F9">
+      <c r="H9">
         <v>462</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,33 +571,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vangled 32A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t xml:space="preserve">9986379</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F10">
+      <c r="H10">
         <v>2031</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -531,33 +631,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Skolevej 5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">7553965</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F11">
+      <c r="H11">
         <v>455</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t xml:space="preserve">310040038</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-05-15</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -581,33 +691,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sønder Nytoft 15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t xml:space="preserve">5128072</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F12">
+      <c r="H12">
         <v>548</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t xml:space="preserve">310040572</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-05-20</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -631,33 +751,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t xml:space="preserve">Kåvervej 27</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t xml:space="preserve">5131186</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F13">
+      <c r="H13">
         <v>262</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t xml:space="preserve">310040585</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-05-20</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -681,33 +811,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t xml:space="preserve">Gammel Byvej 20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t xml:space="preserve">5131840</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="F14">
+      <c r="H14">
         <v>577</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t xml:space="preserve">311001996</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-06-05</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -731,33 +871,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t xml:space="preserve">Stadionvej 14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t xml:space="preserve">5124775</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F15">
+      <c r="H15">
         <v>396</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t xml:space="preserve">311002117</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t xml:space="preserve">2023-06-06</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -781,39 +931,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vangled 32B</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6720</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t xml:space="preserve">9986380</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="F16">
+      <c r="H16">
         <v>1014</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">311064731</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">2024-07-14</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J16"/>
+  <autoFilter ref="A1:L16"/>
 </worksheet>
 </file>
--- a/public/exports/31210917.xlsx
+++ b/public/exports/31210917.xlsx
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 13</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">736938, 5125209</t>
+          <t xml:space="preserve">7553965</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H5">
-        <v>1444</v>
+        <v>254</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -346,11 +346,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H6">
-        <v>254</v>
+        <v>830</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,7 +391,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Stadionvej 13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -401,16 +401,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">7553965</t>
+          <t xml:space="preserve">736938, 5125209</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H7">
-        <v>830</v>
+        <v>1444</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønder Nytoft 15</t>
+          <t xml:space="preserve">Kåvervej 27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5128072</t>
+          <t xml:space="preserve">5131186</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -710,11 +710,11 @@
         </is>
       </c>
       <c r="H12">
-        <v>548</v>
+        <v>262</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">310040572</t>
+          <t xml:space="preserve">310040585</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kåvervej 27</t>
+          <t xml:space="preserve">Sønder Nytoft 15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">5131186</t>
+          <t xml:space="preserve">5128072</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="H13">
-        <v>262</v>
+        <v>548</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">310040585</t>
+          <t xml:space="preserve">310040572</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">

--- a/public/exports/31210917.xlsx
+++ b/public/exports/31210917.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:M16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -659,15 +709,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-05-15</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -719,15 +774,20 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-05-20</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -779,15 +839,20 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-05-20</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -839,15 +904,20 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-06-05</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -899,15 +969,20 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t xml:space="preserve">KEEN MILJØ- &amp; ENERGIRÅDGIVNING ApS</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-06-06</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -959,21 +1034,26 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-07-14</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L16"/>
+  <autoFilter ref="A1:M16"/>
 </worksheet>
 </file>